--- a/markdown_generator/publications.xlsx
+++ b/markdown_generator/publications.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/richardanslow/Documents/Cambridge/richard17a.github.io/markdown_generator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0AEC73F1-1612-AA44-AF39-CF79E2BC0269}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40009_{0EF9F7B7-4371-DE4C-8813-30F5D9437D30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="16460"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>pub_date</t>
   </si>
@@ -49,21 +49,12 @@
     <t>http://academicpages.github.io/files/paper2.pdf</t>
   </si>
   <si>
-    <t>subm.</t>
-  </si>
-  <si>
     <t>Can comets deliver prebiotic molecules to rocky exoplanets?</t>
   </si>
   <si>
     <t>Proceedings of Royal Society A</t>
   </si>
   <si>
-    <t>This paper is about the cometary delivery of prebiotic molecules to rocky exoplanets…</t>
-  </si>
-  <si>
-    <t>in prep.</t>
-  </si>
-  <si>
     <t>WD 0141−675: A case study on how to follow-up astrometric planet candidates around white dwarfs</t>
   </si>
   <si>
@@ -73,9 +64,6 @@
     <t xml:space="preserve">Anslow R. J.,  Bonsor A., Rimmer, P. B. (subm.). "Can comets deliver prebiotic molecules to rocky exoplanets?" &lt;i&gt;Proceedings of Royal Society A&lt;/i&gt;. </t>
   </si>
   <si>
-    <t>tbd.</t>
-  </si>
-  <si>
     <t>Rogers L., Debes J., et al.</t>
   </si>
   <si>
@@ -83,6 +71,12 @@
   </si>
   <si>
     <t>WD-pollution-case-study</t>
+  </si>
+  <si>
+    <t>This paper is about the cometary delivery of prebiotic molecules to rocky exoplanets… This is currently under peer review.</t>
+  </si>
+  <si>
+    <t>tbd. This paper is currently in prep</t>
   </si>
 </sst>
 </file>
@@ -955,46 +949,46 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="1">
+        <v>72686</v>
+      </c>
+      <c r="B2" t="s">
         <v>9</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>10</v>
       </c>
-      <c r="C2" t="s">
-        <v>11</v>
-      </c>
       <c r="D2" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F2" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
-        <v>13</v>
+      <c r="A3" s="1">
+        <v>72686</v>
       </c>
       <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
         <v>14</v>
       </c>
-      <c r="C3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" t="s">
-        <v>18</v>
-      </c>
       <c r="F3" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G3" t="s">
         <v>8</v>

--- a/markdown_generator/publications.xlsx
+++ b/markdown_generator/publications.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/richardanslow/Documents/Cambridge/richard17a.github.io/markdown_generator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40009_{0EF9F7B7-4371-DE4C-8813-30F5D9437D30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40009_{950C9344-35A3-8A4F-97DB-F0A47B55DF04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="16460"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
   <si>
     <t>pub_date</t>
   </si>
@@ -77,6 +77,9 @@
   </si>
   <si>
     <t>tbd. This paper is currently in prep</t>
+  </si>
+  <si>
+    <t>2099-01-01</t>
   </si>
 </sst>
 </file>
@@ -562,7 +565,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -949,8 +952,8 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" s="1">
-        <v>72686</v>
+      <c r="A2" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="B2" t="s">
         <v>9</v>
@@ -972,8 +975,8 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3" s="1">
-        <v>72686</v>
+      <c r="A3" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="B3" t="s">
         <v>11</v>

--- a/markdown_generator/publications.xlsx
+++ b/markdown_generator/publications.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/richardanslow/Documents/Cambridge/richard17a.github.io/markdown_generator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40009_{950C9344-35A3-8A4F-97DB-F0A47B55DF04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40009_{9DEF33CB-F5E3-2243-9CE3-76881B81C5D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="16460"/>
   </bookViews>
@@ -52,9 +52,6 @@
     <t>Can comets deliver prebiotic molecules to rocky exoplanets?</t>
   </si>
   <si>
-    <t>Proceedings of Royal Society A</t>
-  </si>
-  <si>
     <t>WD 0141−675: A case study on how to follow-up astrometric planet candidates around white dwarfs</t>
   </si>
   <si>
@@ -80,6 +77,9 @@
   </si>
   <si>
     <t>2099-01-01</t>
+  </si>
+  <si>
+    <t>Proceedings of the Royal Society A</t>
   </si>
 </sst>
 </file>
@@ -953,22 +953,22 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B2" t="s">
         <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G2" t="s">
         <v>7</v>
@@ -976,22 +976,22 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
         <v>11</v>
       </c>
-      <c r="C3" t="s">
-        <v>12</v>
-      </c>
       <c r="D3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G3" t="s">
         <v>8</v>

--- a/markdown_generator/publications.xlsx
+++ b/markdown_generator/publications.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10409"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/richardanslow/Documents/Cambridge/richard17a.github.io/markdown_generator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40009_{9DEF33CB-F5E3-2243-9CE3-76881B81C5D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{189569E5-02C9-2B4F-9402-E761794D8860}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="16460"/>
+    <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="16460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="publications" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>pub_date</t>
   </si>
@@ -43,50 +43,35 @@
     <t>paper_url</t>
   </si>
   <si>
-    <t>http://academicpages.github.io/files/paper1.pdf</t>
-  </si>
-  <si>
-    <t>http://academicpages.github.io/files/paper2.pdf</t>
-  </si>
-  <si>
     <t>Can comets deliver prebiotic molecules to rocky exoplanets?</t>
   </si>
   <si>
-    <t>WD 0141−675: A case study on how to follow-up astrometric planet candidates around white dwarfs</t>
-  </si>
-  <si>
-    <t>Monthly Notices of the Royal Astronomical Society</t>
-  </si>
-  <si>
     <t xml:space="preserve">Anslow R. J.,  Bonsor A., Rimmer, P. B. (subm.). "Can comets deliver prebiotic molecules to rocky exoplanets?" &lt;i&gt;Proceedings of Royal Society A&lt;/i&gt;. </t>
   </si>
   <si>
-    <t>Rogers L., Debes J., et al.</t>
-  </si>
-  <si>
     <t>exoplanet-cometary-delivery</t>
   </si>
   <si>
-    <t>WD-pollution-case-study</t>
-  </si>
-  <si>
     <t>This paper is about the cometary delivery of prebiotic molecules to rocky exoplanets… This is currently under peer review.</t>
   </si>
   <si>
-    <t>tbd. This paper is currently in prep</t>
-  </si>
-  <si>
-    <t>2099-01-01</t>
-  </si>
-  <si>
     <t>Proceedings of the Royal Society A</t>
+  </si>
+  <si>
+    <t>submitted</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>http://academicpages.github.io/files/exoplanet-cometary-delivery.pdf</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="18" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -217,6 +202,14 @@
     <font>
       <sz val="12"/>
       <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -519,7 +512,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="42">
+  <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
@@ -562,12 +555,14 @@
     <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="42"/>
   </cellXfs>
-  <cellStyles count="42">
+  <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
     <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
@@ -601,6 +596,7 @@
     <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
     <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
     <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Hyperlink" xfId="42" builtinId="8"/>
     <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
     <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
     <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
@@ -920,84 +916,71 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="18.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B2" t="s">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="1"/>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="H2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="G2" t="s">
-        <v>7</v>
-      </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" t="s">
-        <v>8</v>
-      </c>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B3" s="1"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1" xr:uid="{BDDC3312-1FC5-CD4F-B7F1-98EF41D47FC5}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/markdown_generator/publications.xlsx
+++ b/markdown_generator/publications.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/richardanslow/Documents/Cambridge/richard17a.github.io/markdown_generator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{189569E5-02C9-2B4F-9402-E761794D8860}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADD954D6-20FE-ED4C-BB46-9535990C3723}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="16460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,9 +46,6 @@
     <t>Can comets deliver prebiotic molecules to rocky exoplanets?</t>
   </si>
   <si>
-    <t xml:space="preserve">Anslow R. J.,  Bonsor A., Rimmer, P. B. (subm.). "Can comets deliver prebiotic molecules to rocky exoplanets?" &lt;i&gt;Proceedings of Royal Society A&lt;/i&gt;. </t>
-  </si>
-  <si>
     <t>exoplanet-cometary-delivery</t>
   </si>
   <si>
@@ -64,7 +61,10 @@
     <t>Y</t>
   </si>
   <si>
-    <t>http://academicpages.github.io/files/exoplanet-cometary-delivery.pdf</t>
+    <t>http://richard17a.github.io/files/exoplanet-cometary-delivery.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anslow R. J.,  Bonsor A., Rimmer, P. B. (subm.). "Can comets deliver prebiotic molecules to rocky exoplanets?" &lt;i&gt;Proceedings of the Royal Society A&lt;/i&gt;. </t>
   </si>
 </sst>
 </file>
@@ -926,7 +926,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -952,26 +952,26 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" t="s">
         <v>7</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" t="s">
         <v>8</v>
       </c>
-      <c r="G2" t="s">
-        <v>9</v>
-      </c>
       <c r="H2" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">

--- a/markdown_generator/publications.xlsx
+++ b/markdown_generator/publications.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/richardanslow/Documents/Cambridge/richard17a.github.io/markdown_generator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADD954D6-20FE-ED4C-BB46-9535990C3723}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A9B7E2A-FA0B-284B-A629-FA742DD4AB79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="16460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/markdown_generator/publications.xlsx
+++ b/markdown_generator/publications.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/richardanslow/Documents/Cambridge/richard17a.github.io/markdown_generator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A9B7E2A-FA0B-284B-A629-FA742DD4AB79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37F9AA54-0B90-4442-A7A7-CD89BDD5EB08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="16460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/markdown_generator/publications.xlsx
+++ b/markdown_generator/publications.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/richardanslow/Documents/Cambridge/richard17a.github.io/markdown_generator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37F9AA54-0B90-4442-A7A7-CD89BDD5EB08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53C2DC0D-B818-DE4D-B967-AD2BF0491428}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="16460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
